--- a/AAII_Financials/Yearly/CSLLY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CSLLY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>CSLLY</t>
   </si>
@@ -656,149 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43281</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15797000</v>
+      </c>
+      <c r="E8" s="3">
         <v>15558000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14800000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13310000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10562000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10310000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9150800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8538600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7915300</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7722000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7479000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7095000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6314000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4830000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4466700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3924400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3761200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3531600</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8075000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8079000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7705000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6996000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5732000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5843300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5226400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4777400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4383700</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -811,38 +823,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1223000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1359000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1428000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1266000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1156000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1001400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>921800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>831800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>702400</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -870,23 +886,26 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>7928000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-26000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>84000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>365000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
@@ -900,39 +919,45 @@
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>837000</v>
+      </c>
+      <c r="E15" s="3">
         <v>805000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>722000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>623000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>357000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>323200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>279300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>310400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>253500</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -942,68 +967,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11556000</v>
+      </c>
+      <c r="E17" s="3">
         <v>11454000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10904000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9888000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7635000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7180000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6434300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6034600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5535000</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4241000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4104000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3896000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3422000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2927000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3130000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2716500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2504000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2380300</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1016,8 +1048,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1027,147 +1060,162 @@
       <c r="E20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3">
         <v>22000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-13000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>12100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>48900</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5078000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4909000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4618000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4023000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3297000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3441100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2987400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2765500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2633800</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>430000</v>
+      </c>
+      <c r="E22" s="3">
         <v>444000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>476000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>410000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>178000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>158700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>142400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>127800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>108400</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4087000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3724000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3375000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2663000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2780000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2963100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2572700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2341100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2281200</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1101000</v>
+      </c>
+      <c r="E24" s="3">
         <v>588000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>661000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>419000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>525000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>588100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>470200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>422400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>552300</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1195,69 +1243,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2986000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3136000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2714000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2244000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2255000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2375000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2102500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1918700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1728900</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2579000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3002000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2642000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2194000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2255000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2375000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2102500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1918700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1728900</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1285,9 +1342,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1315,9 +1375,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1345,9 +1408,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1375,9 +1441,12 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1387,57 +1456,63 @@
       <c r="E32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3">
         <v>-22000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>13000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-12100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-48900</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2579000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3002000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2642000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2194000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2255000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2375000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2102500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1918700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1728900</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1465,74 +1540,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2579000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3002000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2642000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2194000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2255000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2375000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2102500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1918700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1728900</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43281</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1545,8 +1629,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1559,38 +1644,42 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1513000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2157000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1657000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1548000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10436000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1808800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1194400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>657800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>814700</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1616,131 +1705,146 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>1600</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3353000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2968000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2767000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1936000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1513000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1648000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1593300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1726300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1372100</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6627000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6466000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5964000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5466000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4333000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3780600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3509500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3038800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2692800</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3">
         <v>126000</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11832000</v>
+      </c>
+      <c r="E46" s="3">
         <v>11850000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10768000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9259000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16461000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7389700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6446200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5540100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4993700</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1765,72 +1869,81 @@
       <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L47" s="3">
         <v>6200</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8213000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9797000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9658000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9352000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8309000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7536000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6305400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4484300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3551400</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10964000</v>
+      </c>
+      <c r="E49" s="3">
         <v>16185000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16346000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16446000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2638000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2669700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2291000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1878300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1802500</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1858,9 +1971,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1888,39 +2004,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>411000</v>
+      </c>
+      <c r="E52" s="3">
         <v>481000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>339000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>275000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>420000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>32000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>33000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19400</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1948,39 +2070,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33646000</v>
+      </c>
+      <c r="E54" s="3">
         <v>39404000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>38022000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36234000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28346000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18156900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15615500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12314400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10774500</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1993,8 +2121,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2007,188 +2136,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>839000</v>
+      </c>
+      <c r="E57" s="3">
         <v>808000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>867000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>820000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>592000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>523000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>458300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>422600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>417400</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1142000</v>
+      </c>
+      <c r="E58" s="3">
         <v>804000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>944000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1055000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4494000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>473800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>202300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>420600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>225700</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>346000</v>
+      </c>
+      <c r="E59" s="3">
         <v>316000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>448000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>360000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>141000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>328700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>257700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>229500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>315900</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5354000</v>
+      </c>
+      <c r="E60" s="3">
         <v>4815000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4950000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4608000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7108000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3103600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2141500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2188200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1914700</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9754000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10694000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11239000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11172000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5165000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5333100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5790500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4242200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4160600</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>705000</v>
+      </c>
+      <c r="E62" s="3">
         <v>612000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>584000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>900000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>596000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>545200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>341600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>86500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>126900</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2216,9 +2364,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,9 +2397,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2276,39 +2430,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17339000</v>
+      </c>
+      <c r="E66" s="3">
         <v>17997000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18621000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18408000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13769000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9775600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9087900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7063100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6694600</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2321,8 +2481,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2350,9 +2511,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2380,9 +2544,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2410,9 +2577,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2440,39 +2610,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13698000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17744000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16012000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14621000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13504000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12252700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10752300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9612300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8490200</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2500,9 +2676,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2530,9 +2709,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2560,39 +2742,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14797000</v>
+      </c>
+      <c r="E76" s="3">
         <v>19335000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17363000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15786000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14577000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8381300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6527600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5251300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4079900</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2620,74 +2808,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43281</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2579000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3002000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2642000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2194000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2255000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2375000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2102500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1918700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1728900</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2700,38 +2897,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>555000</v>
+      </c>
+      <c r="E83" s="3">
         <v>549000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>528000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>490000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>445000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>399400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>347300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>273200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>238900</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2759,9 +2960,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2789,9 +2993,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2819,9 +3026,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2849,9 +3059,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2879,39 +3092,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3512000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3561000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2764000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2601000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2629000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3621900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2488300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1644400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1902100</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2924,38 +3143,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-646000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-636000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-847000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1228000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1079000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1196300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1206800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1117600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-778800</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2983,9 +3206,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3013,39 +3239,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1271000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-850000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1259000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11843000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1636000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1673200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1366700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1287300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1534100</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3058,38 +3290,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1412000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1334000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1192000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1085000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1039000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>958000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>883100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>806800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>672200</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3117,9 +3353,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3147,9 +3386,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3177,97 +3419,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2828000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2241000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1284000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>456000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7676000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1401800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-642700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-491500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-371500</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E101" s="3">
         <v>44000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-87000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-39000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-65000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>31900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>14600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-20500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-26800</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-644000</v>
+      </c>
+      <c r="E102" s="3">
         <v>514000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>134000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8825000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8604000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>578800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>493500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-154900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-30300</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
